--- a/artfynd/A 34275-2025 artfynd.xlsx
+++ b/artfynd/A 34275-2025 artfynd.xlsx
@@ -1552,7 +1552,7 @@
         <v>126600693</v>
       </c>
       <c r="B9" t="n">
-        <v>4775</v>
+        <v>4777</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>126600738</v>
       </c>
       <c r="B10" t="n">
-        <v>4775</v>
+        <v>4777</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>126600768</v>
       </c>
       <c r="B11" t="n">
-        <v>4775</v>
+        <v>4777</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>126600779</v>
       </c>
       <c r="B12" t="n">
-        <v>4775</v>
+        <v>4777</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34275-2025 artfynd.xlsx
+++ b/artfynd/A 34275-2025 artfynd.xlsx
@@ -1581,11 +1581,7 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1693,11 +1689,7 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1805,11 +1797,7 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1917,11 +1905,7 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>

--- a/artfynd/A 34275-2025 artfynd.xlsx
+++ b/artfynd/A 34275-2025 artfynd.xlsx
@@ -1552,7 +1552,7 @@
         <v>126600693</v>
       </c>
       <c r="B9" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>126600738</v>
       </c>
       <c r="B10" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>126600768</v>
       </c>
       <c r="B11" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         <v>126600779</v>
       </c>
       <c r="B12" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
